--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
   <si>
     <t>name</t>
   </si>
@@ -304,14 +304,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dropDomain，指定域名为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，不指定域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>语法：db.createDomain(&lt; name &gt;,&lt; groups &gt;,[ options ])
 参数规格：
 name：string，必填，全局唯一，参数规则资料没给说明，参考createCS：不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
@@ -326,23 +318,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，删除域，域名为空串，如：
-db.dropDomain("")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除域，不指定域名，如：
-db.dropDomain()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域创建失败，提示参数不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>语法：db.getDomain(&lt; name &gt;)
 参数规格：
 name：string，必填，获取已存在的域。不能获取系统域。</t>
@@ -355,17 +330,219 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、不存在的域
-3、空串，如db.getDomain(“”)
-4、不指定域，如db.getDomain()</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>getDomain，获取不存在的域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getDomain，指定的域名为空串</t>
+    <t>dropDomain，指定域名为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除域，域名为空，覆盖如下取值：
+db.dropDomain("")
+db.dropDomain()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getDomain，指定的域名为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域获取失败，提示域不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域获取失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listDomains，加条件查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.listDomains()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定的域，域名为空，覆盖如下取值：
+db.getDomain("")
+db.getDomain()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域获取成功，指定的域被直接忽略，返回结果显示所有域（非系统域）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取所有域（非系统域），指定域名，覆盖如下取值：
+  a.指定已存在的域名
+  b.空串
+如：
+db.listDomains("dm")
+db.listDomains("")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：domain.alter(&lt; options &gt;)，必须指定一个参数
+参数规格：
+options:Groups，删除复制组前必须保证其不包含任何数据。
+options:Autosplit，bool类型，true|false，非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域修改失败，提示rg4不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域修改失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter，指定Groups和AutoSplit参数正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter，Groups指定不存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter，Groups为空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1','rg2']，AutoSplit:true)
+2、修改域，Groups和AutoSplit修改正确，覆盖如下取值：
+  a.Groups指定所有组，AutoSplit:true
+  b.AutoSplit:false
+如：
+domain.alter({Groups:['rg1','rg2','rg3']},{AutoSplit:true})
+domain.alter({AutoSplit:false})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域修改成功，db.listDomains()查看域修改正确
+2、做如下操作，检查域修改后是否正确可用，如：
+  创建CS，并指定域为domain
+  创建CL，不指定AutoSplit，指定为hash切分
+  插入批量数据
+若修改后域为自动切分，则数据按均匀落在不同的组，域修改正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、修改dm域，Groups指定不存在的组，如：
+domain.alter({Groups:['rg2','rg4']})，其中rg4为不存在的组
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、修改域，Groups指定为空串，如：
+domain.alter({Groups:['']})
+domain.alter({Groups:})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter，AutoSplit取值非bool型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter，AutoSplit为空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、修改域，AutoSplit取值非法，如：
+domain.alter({AutoSplit:test})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、修改域，AutoSplit为空串，如：
+domain.alter({AutoSplit:})
+domain.alter({AutoSplit:''})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.alter，不指定任何参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、修改域，不指定任何参数，如：
+domain.alter()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.listCollections，加条件查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：domain.listCollections()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：domain.listCollectionSpaces()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain.listCollectionSpaces，加条件查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、集合获取成功，指定的CS被直接忽略，返回结果显示该域中的所有CS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、集合获取成功，指定的CL被直接忽略，返回结果显示该域中的所有CL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、创建CS，指定域为domain
+3、在CS创建CL
+4、domain.listCollections获取域中所有集合，指定集合名词，覆盖如下取值：
+  a.指定已存在的集合
+  b.空串
+如：
+domain.listCollections("testCL")
+domain.listCollections("")
+5、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1'])
+2、创建CS，指定域为domain
+3、domain.listCollections获取域中所有集合空间，指定集合空间名词，覆盖如下取值：
+  a.指定已存在的集合空间
+  b.空串
+如：
+domain.listCollectionSpaces("testCS")
+domain.listCollectionSpaces("")
+4、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -453,7 +630,7 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -474,7 +651,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" relativeIndent="255" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
@@ -536,34 +713,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I52" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I27" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I27"/>
   <tableColumns count="9">
-    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="2">
+    <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="0">
+    <tableColumn id="2" uniqueName="summary" name="summary" dataDxfId="7">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/summary" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="1">
+    <tableColumn id="3" uniqueName="preconditions" name="preconditions" dataDxfId="6">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/preconditions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="8">
+    <tableColumn id="4" uniqueName="execution_type" name="execution_type" dataDxfId="5">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/execution_type" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="7">
+    <tableColumn id="5" uniqueName="importance" name="importance" dataDxfId="4">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/importance" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="6">
+    <tableColumn id="6" uniqueName="step_number" name="step_number" dataDxfId="3">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/step_number" xmlDataType="integer"/>
     </tableColumn>
-    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="5">
+    <tableColumn id="7" uniqueName="actions" name="actions" dataDxfId="2">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/actions" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="4">
+    <tableColumn id="8" uniqueName="expectedresults" name="expectedresults" dataDxfId="1">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/expectedresults" xmlDataType="string"/>
     </tableColumn>
-    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="3">
+    <tableColumn id="9" uniqueName="execution_type" name="execution_type2" dataDxfId="0">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/steps/step/execution_type" xmlDataType="integer"/>
     </tableColumn>
   </tableColumns>
@@ -856,10 +1033,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="24.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="5" customWidth="1"/>
     <col min="3" max="3" width="22.25" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
@@ -932,7 +1109,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -1142,7 +1319,7 @@
         <v>45</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
@@ -1197,9 +1374,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="54">
+    <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>16</v>
@@ -1208,15 +1385,18 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="67.5">
+      <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="54">
-      <c r="A17" s="2" t="s">
-        <v>55</v>
+      <c r="B17" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>16</v>
@@ -1225,249 +1405,205 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="67.5">
       <c r="A18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="108">
+      <c r="A19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="27">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D19" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="175.5">
+      <c r="A20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="94.5">
+      <c r="A21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="94.5">
+      <c r="A22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="81">
+      <c r="A23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="40.5">
-      <c r="A24" s="2"/>
-      <c r="B24" s="5" t="s">
-        <v>63</v>
+      <c r="G23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="94.5">
+      <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D24" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="81">
+      <c r="A25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D25" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="162">
+      <c r="A26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="175.5">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="D27" s="4">
         <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="2"/>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="2"/>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="2"/>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="2"/>
-      <c r="D31" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="2"/>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2"/>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2"/>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2"/>
-      <c r="D35" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="2"/>
-      <c r="D36" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="2"/>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="2"/>
-      <c r="D38" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="2"/>
-      <c r="D39" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="2"/>
-      <c r="D40" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="2"/>
-      <c r="D41" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="2"/>
-      <c r="D42" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="2"/>
-      <c r="D43" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="2"/>
-      <c r="D44" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="2"/>
-      <c r="D45" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="2"/>
-      <c r="D46" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="2"/>
-      <c r="D47" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2"/>
-      <c r="D48" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="2"/>
-      <c r="D49" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="2"/>
-      <c r="D50" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="2"/>
-      <c r="D51" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="2"/>
-      <c r="D52" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="2"/>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="2"/>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="2"/>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
@@ -126,14 +126,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，创建域，输入name长度无效，覆盖如下无效取值：
-  a.空串
-  b.128字节
-如：
-db.createDomain('',['rg1'])
-3、检查执行结果</t>
-  </si>
-  <si>
     <t>1、域创建失败，提示参数超出长度，提示信息合理准确
 2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,40 +186,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，创建域，输入name、groups、AutoSplit有效参数创建域，规格如下：
-name覆盖如下取值：
-  a.1字节的有效字符，如：a 或 *
-  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#$%^&amp;*()_+-=\][{}|,./&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~._.....127B”
-groups覆盖如下数值个数：1、10（没限制，随机取值）
-Autosplit覆盖如下取值:
-   a.AutoSplit:true|false
-   b.不指定AutoSplit
-   c.AutoSplit：yes|no、T|F、0|-1、Y|N
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，AutoSplit取值非法，覆盖如下取值：
-  a.非bool型取值，如test_123
-  b.空串
-如：
-db.createDomain('dm',['rg1']),{AutoSplit:test_123})
-db.createDomain('dm',['rg1']),{AutoSplit:)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>createDomain，格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，参数格式错误，覆盖如下参数格式：
-  a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
-  b.多参数
-如：
-db.createDomain(dm,[rg1],{AutoSplit:"true"})
-db.createDomain('dm',['rg1']),{AutoSplit:true,true)
-2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -324,12 +283,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，获取指定域，不指定域名，如：
-db.dropDomain()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>getDomain，获取不存在的域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -346,11 +299,6 @@
   </si>
   <si>
     <t>getDomain，指定的域名为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域获取失败，提示域不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -543,6 +491,57 @@
 domain.listCollectionSpaces("testCS")
 domain.listCollectionSpaces("")
 4、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，输入name、groups、AutoSplit有效参数创建域，规格如下：
+name覆盖如下取值：
+  a.1字节的有效字符，如：a 或 *
+  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#%^&amp;*()_+-=\][{}|,/&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~_127B”
+groups覆盖如下数值个数：1、10（没限制，随机取值）
+Autosplit覆盖如下取值:
+   a.AutoSplit:true|false
+   b.不指定AutoSplit
+   c.AutoSplit：yes|no、T|F、0|-1、Y|N
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，输入name长度无效，覆盖如下无效取值：
+  a.空串
+  b.128字节
+如：
+db.createDomain('',['rg1']) 或  db.createDomain()  或  为128字节的有效字符
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，AutoSplit取值非法，覆盖如下取值：
+  a.非bool型取值，如test_123
+  b.空串
+如：
+db.createDomain('dm',['rg1'],{AutoSplit:test_123})
+db.createDomain('dm',['rg1'],{AutoSplit:)
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，参数格式错误，覆盖如下参数格式：
+  a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
+  b.多参数
+如：
+db.createDomain(dm,[rg1],{AutoSplit:"true"})
+db.createDomain('dm',['rg1'],{AutoSplit:true,true)
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、域获取失败，提示dm在sdb不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定域，不指定域名，如：
+db.dropDomain('dm')，其中dm在sdb不存在
+2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1080,7 +1079,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1109,7 +1108,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -1124,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -1166,14 +1165,14 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
+    <row r="6" spans="1:9" ht="121.5">
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1187,10 +1186,10 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1207,16 +1206,16 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="54">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -1227,16 +1226,16 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="54">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -1247,16 +1246,16 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="54">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>16</v>
@@ -1267,16 +1266,16 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="135">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
@@ -1287,16 +1286,16 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" ht="148.5">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>16</v>
@@ -1307,19 +1306,19 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="81">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
@@ -1330,16 +1329,16 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="54">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
@@ -1350,16 +1349,16 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="54">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>16</v>
@@ -1368,15 +1367,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>16</v>
@@ -1385,18 +1384,18 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="67.5">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>16</v>
@@ -1405,15 +1404,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>16</v>
@@ -1422,18 +1421,18 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="108">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>16</v>
@@ -1442,35 +1441,35 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="175.5">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="H20" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="94.5">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>16</v>
@@ -1479,15 +1478,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="94.5">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>16</v>
@@ -1496,15 +1495,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="81">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
@@ -1513,15 +1512,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="94.5">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
@@ -1530,15 +1529,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="81">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>16</v>
@@ -1547,18 +1546,18 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="162">
       <c r="A26" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>16</v>
@@ -1567,30 +1566,30 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="175.5">
       <c r="A27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:8">

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="94">
   <si>
     <t>name</t>
   </si>
@@ -204,11 +204,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、域创建失败，提示域不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dropDomain，删除非空的域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -216,11 +211,6 @@
     <t>1、进入sdb，删除非空的域，如：
 db.dropDomain("test"),其中test中存在CS
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域创建失败，提示域非空，提示信息合理准确
-2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -258,11 +248,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、域创建失败，提示系统域不能删除，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>语法：db.createDomain(&lt; name &gt;,&lt; groups &gt;,[ options ])
 参数规格：
 name：string，必填，全局唯一，参数规则资料没给说明，参考createCS：不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
@@ -534,14 +519,34 @@
 2、检查执行结果</t>
   </si>
   <si>
-    <t>1、域获取失败，提示dm在sdb不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，获取指定域，不指定域名，如：
 db.dropDomain('dm')，其中dm在sdb不存在
 2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示域不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示域非空，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示系统域不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示dm在sdb不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1108,7 +1113,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -1123,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -1186,7 +1191,7 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>27</v>
@@ -1286,7 +1291,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>31</v>
@@ -1306,7 +1311,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>31</v>
@@ -1318,7 +1323,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
@@ -1332,13 +1337,13 @@
         <v>42</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="54">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
@@ -1349,16 +1354,16 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="54">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>16</v>
@@ -1367,15 +1372,15 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>16</v>
@@ -1384,18 +1389,18 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="67.5">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>16</v>
@@ -1404,15 +1409,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>16</v>
@@ -1421,55 +1426,55 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="108">
       <c r="A19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="175.5">
       <c r="A20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="H20" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="94.5">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>16</v>
@@ -1478,15 +1483,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="94.5">
       <c r="A22" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>16</v>
@@ -1495,15 +1500,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="81">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
@@ -1512,15 +1517,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="94.5">
       <c r="A24" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
@@ -1529,15 +1534,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="81">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>16</v>
@@ -1546,18 +1551,18 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="162">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>16</v>
@@ -1566,18 +1571,18 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="175.5">
       <c r="A27" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>16</v>
@@ -1586,10 +1591,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:8">

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（Domain）参数校验测试用例.xlsx
@@ -13,6 +13,116 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+domain</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>和</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>cl</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>都不设置</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>autosplit</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>，查看</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>cl</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>属性是否为自动切分</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> --hash</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="testcase" type="4" refreshedVersion="0" background="1">
@@ -89,14 +199,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createDomain，覆盖name/groups/options有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，name重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建域，输入有效的name、groups、Autosplit创建域，如：
 db.createDomain('dm',['rg1','rg2'],{AutoSplit:true})
 2、重复步骤1，创建name相同的域
@@ -109,29 +211,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createDomain，name字符无效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、域创建失败，提示参数不合法，提示信息合理准确
 2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createDomain，name长度无效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，name参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、域创建失败，提示参数超出长度，提示信息合理准确
 2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，groups指定的组不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -164,37 +250,17 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createDomain，groups取值为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建域，groups取值为空串，如：
 db.createDomain('dm',[''])
 2、检查执行结果</t>
   </si>
   <si>
-    <t>createDomain，groups参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建域，groups参数不存在，如：
 db.createDomain('dm',{AutoSplit:true})
 2、检查执行结果</t>
   </si>
   <si>
-    <t>createDomain，options:AutoSplit取值非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>测试用例摘要（测试目的）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，删除不存在的域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -204,17 +270,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dropDomain，删除非空的域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，删除非空的域，如：
 db.dropDomain("test"),其中test中存在CS
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，删除系统域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -268,14 +326,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getDomain，获取不存在的域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，指定域名为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，删除域，域名为空，覆盖如下取值：
 db.dropDomain("")
 db.dropDomain()
@@ -283,16 +333,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getDomain，指定的域名为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、域获取失败，提示参数错误，提示信息合理准确
 2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listDomains，加条件查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -339,30 +381,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>domain.alter，指定Groups和AutoSplit参数正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，Groups指定不存在的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，Groups为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1','rg2']，AutoSplit:true)
-2、修改域，Groups和AutoSplit修改正确，覆盖如下取值：
-  a.Groups指定所有组，AutoSplit:true
-  b.AutoSplit:false
-如：
-domain.alter({Groups:['rg1','rg2','rg3']},{AutoSplit:true})
-domain.alter({AutoSplit:false})
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、域修改成功，db.listDomains()查看域修改正确
 2、做如下操作，检查域修改后是否正确可用，如：
   创建CS，并指定域为domain
@@ -389,14 +407,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>domain.alter，AutoSplit取值非bool型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，AutoSplit为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建域，如：
 var domain = db.createDomain('domain',['rg1'])
 2、修改域，AutoSplit取值非法，如：
@@ -414,10 +424,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>domain.alter，不指定任何参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建域，如：
 var domain = db.createDomain('domain',['rg1'])
 2、修改域，不指定任何参数，如：
@@ -426,10 +432,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>domain.listCollections，加条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>语法：domain.listCollections()
 无参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -437,10 +439,6 @@
   <si>
     <t>语法：domain.listCollectionSpaces()
 无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.listCollectionSpaces，加条件查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -479,6 +477,46 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1、进入sdb，创建域，输入name长度无效，覆盖如下无效取值：
+  a.空串
+  b.128字节
+如：
+db.createDomain('',['rg1']) 或  db.createDomain()  或  为128字节的有效字符
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定域，不指定域名，如：
+db.dropDomain('dm')，其中dm在sdb不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示域不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示域非空，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示系统域不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、域删除失败，提示dm在sdb不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1、进入sdb，创建域，输入name、groups、AutoSplit有效参数创建域，规格如下：
 name覆盖如下取值：
   a.1字节的有效字符，如：a 或 *
@@ -492,15 +530,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，创建域，输入name长度无效，覆盖如下无效取值：
-  a.空串
-  b.128字节
-如：
-db.createDomain('',['rg1']) 或  db.createDomain()  或  为128字节的有效字符
-3、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，创建域，AutoSplit取值非法，覆盖如下取值：
   a.非bool型取值，如test_123
   b.空串
@@ -508,6 +537,7 @@
 db.createDomain('dm',['rg1'],{AutoSplit:test_123})
 db.createDomain('dm',['rg1'],{AutoSplit:)
 2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，创建域，参数格式错误，覆盖如下参数格式：
@@ -517,44 +547,101 @@
 db.createDomain(dm,[rg1],{AutoSplit:"true"})
 db.createDomain('dm',['rg1'],{AutoSplit:true,true)
 2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定域，不指定域名，如：
-db.dropDomain('dm')，其中dm在sdb不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域删除失败，提示域不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域删除失败，提示域非空，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域删除失败，提示系统域不能删除，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域删除失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域删除失败，提示dm在sdb不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建域，如：
+var domain = db.createDomain('domain',['rg1','rg2']，AutoSplit:true)
+2、修改域，Groups和AutoSplit修改正确，覆盖如下取值：
+  a.Groups指定所有组（建议10个），AutoSplit:true
+  b.AutoSplit:false
+如：
+domain.alter({Groups:['rg1','rg2','rg3']},{AutoSplit:true})
+domain.alter({AutoSplit:false})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createDomain，覆盖name/groups/options有效字符和边界_st.verify.domain.001</t>
+  </si>
+  <si>
+    <t>createDomain，name重复_st.verify.domain.002</t>
+  </si>
+  <si>
+    <t>createDomain，name字符无效_st.verify.domain.003</t>
+  </si>
+  <si>
+    <t>createDomain，name长度无效_st.verify.domain.004</t>
+  </si>
+  <si>
+    <t>createDomain，name参数不存在_st.verify.domain.005</t>
+  </si>
+  <si>
+    <t>createDomain，groups指定的组不存在_st.verify.domain.006</t>
+  </si>
+  <si>
+    <t>createDomain，groups取值为空串_st.verify.domain.007</t>
+  </si>
+  <si>
+    <t>createDomain，groups参数不存在_st.verify.domain.008</t>
+  </si>
+  <si>
+    <t>createDomain，options:AutoSplit取值非法_st.verify.domain.009</t>
+  </si>
+  <si>
+    <t>createDomain，格式错误_st.verify.domain.010</t>
+  </si>
+  <si>
+    <t>dropDomain，删除不存在的域_st.verify.domain.011</t>
+  </si>
+  <si>
+    <t>dropDomain，删除非空的域_st.verify.domain.012</t>
+  </si>
+  <si>
+    <t>dropDomain，删除系统域_st.verify.domain.013</t>
+  </si>
+  <si>
+    <t>dropDomain，指定域名为空_st.verify.domain.014</t>
+  </si>
+  <si>
+    <t>getDomain，获取不存在的域_st.verify.domain.015</t>
+  </si>
+  <si>
+    <t>getDomain，指定的域名为空_st.verify.domain.016</t>
+  </si>
+  <si>
+    <t>listDomains，加条件查询_st.verify.domain.017</t>
+  </si>
+  <si>
+    <t>domain.alter，指定Groups和AutoSplit参数正确_st.verify.domain.018</t>
+  </si>
+  <si>
+    <t>domain.alter，Groups指定不存在的组_st.verify.domain.019</t>
+  </si>
+  <si>
+    <t>domain.alter，Groups为空串_st.verify.domain.020</t>
+  </si>
+  <si>
+    <t>domain.alter，AutoSplit取值非bool型_st.verify.domain.021</t>
+  </si>
+  <si>
+    <t>domain.alter，AutoSplit为空串_st.verify.domain.022</t>
+  </si>
+  <si>
+    <t>domain.alter，不指定任何参数_st.verify.domain.023</t>
+  </si>
+  <si>
+    <t>domain.listCollectionSpaces，加条件查询_st.verify.domain.024</t>
+  </si>
+  <si>
+    <t>domain.listCollections，加条件查询_st.verify.domain.025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,6 +667,26 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1046,7 +1153,7 @@
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="41" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1084,7 +1191,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1110,10 +1217,10 @@
     </row>
     <row r="3" spans="1:9" ht="256.5">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
@@ -1122,13 +1229,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>18</v>
@@ -1139,47 +1246,59 @@
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="108">
       <c r="A5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="121.5">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="1" t="s">
@@ -1188,19 +1307,25 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="54">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -1208,19 +1333,25 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="54">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -1228,19 +1359,25 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="54">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -1248,19 +1385,25 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="54">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>16</v>
@@ -1268,19 +1411,25 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="135">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
@@ -1288,19 +1437,25 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="148.5">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>16</v>
@@ -1308,22 +1463,28 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="81">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
@@ -1331,19 +1492,25 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="54">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
@@ -1351,19 +1518,25 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="54">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>16</v>
@@ -1371,250 +1544,368 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>62</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="67.5">
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="67.5">
+      <c r="A18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="108">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="189">
+      <c r="A20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="94.5">
+      <c r="A21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="94.5">
+      <c r="A22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="81">
+      <c r="A23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="94.5">
+      <c r="A24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="81">
+      <c r="A25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="162">
+      <c r="A26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="175.5">
+      <c r="A27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="67.5">
-      <c r="A17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="67.5">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="108">
-      <c r="A19" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="175.5">
-      <c r="A20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="94.5">
-      <c r="A21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="94.5">
-      <c r="A22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="81">
-      <c r="A23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="94.5">
-      <c r="A24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="81">
-      <c r="A25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="162">
-      <c r="A26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="175.5">
-      <c r="A27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:9">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:9">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:9">
       <c r="A31" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>